--- a/artfynd/A 7730-2024 artfynd.xlsx
+++ b/artfynd/A 7730-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,6 +922,3069 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>115100122</v>
+      </c>
+      <c r="B4" t="n">
+        <v>94339</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>306077</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6511820</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>115100117</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>305964</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6511834</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3 exemplar</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>115100098</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>305845</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6511605</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>115100107</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>306095</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6511807</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>15 exemplar</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>115100123</v>
+      </c>
+      <c r="B8" t="n">
+        <v>94339</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>305968</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6511761</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>115100112</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>305959</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6511815</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>85 exemplar</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>115100114</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>305964</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6511829</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>40 exemplar</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>115100090</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93979</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>305966</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6511824</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>115100092</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>306080</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6511824</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>115100087</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93979</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>305701</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6511780</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>115100110</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>306049</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6511839</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ca 210 exemplar</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>115100108</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>305903</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6511685</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ca 600 exemplar</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>115100096</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>305960</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6511731</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>115100101</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96520</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>305742</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6511809</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>115100113</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>305910</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6511695</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>70 exemplar</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>115100095</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>305862</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6511945</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>115100094</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>305813</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6511609</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>115100099</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>305980</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6511806</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>115100118</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80078</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>306083</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6511831</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>115100116</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>305917</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6511677</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>7 exemplar</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>115100091</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57388</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>306089</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6511822</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2 individer observerade + läte</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>115100097</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>305884</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6511635</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>115100093</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>305918</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6511660</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>115100088</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93979</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>306101</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6511831</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>115100115</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>305971</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6511831</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>35 exemplar</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>115100089</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93979</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>305965</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6511837</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>115100109</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>306096</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6511810</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ca 280 exemplar</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>115100105</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>305995</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6511833</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ca 160 exemplar</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>115100121</v>
+      </c>
+      <c r="B32" t="n">
+        <v>94339</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Pulsehagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>306216</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6511693</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
